--- a/artfynd/A 2295-2026 artfynd.xlsx
+++ b/artfynd/A 2295-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288129</v>
       </c>
       <c r="B4" t="n">
-        <v>79873</v>
+        <v>79879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131288044</v>
       </c>
       <c r="B5" t="n">
-        <v>91785</v>
+        <v>91791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2295-2026 artfynd.xlsx
+++ b/artfynd/A 2295-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288129</v>
       </c>
       <c r="B4" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131288044</v>
       </c>
       <c r="B5" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2295-2026 artfynd.xlsx
+++ b/artfynd/A 2295-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288129</v>
       </c>
       <c r="B4" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131288044</v>
       </c>
       <c r="B5" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2295-2026 artfynd.xlsx
+++ b/artfynd/A 2295-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288129</v>
       </c>
       <c r="B4" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>131288044</v>
       </c>
       <c r="B5" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2295-2026 artfynd.xlsx
+++ b/artfynd/A 2295-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131288076</v>
+        <v>131288044</v>
       </c>
       <c r="B2" t="n">
-        <v>57092</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512514</v>
+        <v>512519</v>
       </c>
       <c r="R2" t="n">
-        <v>6697021</v>
+        <v>6697017</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +751,13 @@
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre tall, betad i kronan.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131288038</v>
+        <v>131288129</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,19 +787,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -819,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512530</v>
+        <v>512396</v>
       </c>
       <c r="R3" t="n">
-        <v>6697034</v>
+        <v>6696911</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,48 +877,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131288129</v>
+        <v>70154425</v>
       </c>
       <c r="B4" t="n">
-        <v>79885</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Smedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512396</v>
+        <v>512364</v>
       </c>
       <c r="R4" t="n">
-        <v>6696911</v>
+        <v>6697041</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -950,12 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2018-03-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tjädertallar flera i äldre fin barrblandskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,29 +968,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131288044</v>
+        <v>70154486</v>
       </c>
       <c r="B5" t="n">
-        <v>91801</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,37 +997,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Smedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512519</v>
+        <v>512421</v>
       </c>
       <c r="R5" t="n">
-        <v>6697017</v>
+        <v>6697066</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1051,12 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1065,22 +1080,240 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>70154500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Smedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>512207</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6696934</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-03-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-03-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Under tjädertall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131288076</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Smedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512514</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6697021</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre tall, betad i kronan.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2295-2026 artfynd.xlsx
+++ b/artfynd/A 2295-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131288044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131288129</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70154425</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70154486</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70154500</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,8 +1344,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131288076</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>